--- a/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">

--- a/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
